--- a/thaco/design/Office-1 v2.xlsx
+++ b/thaco/design/Office-1 v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/design/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00E8D6E8-C59B-FD4B-81DC-4A7430BB0A0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E61468CE-498A-6745-A2EB-CBBC7BEC798B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38560" yWindow="660" windowWidth="38080" windowHeight="20780" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38860" yWindow="500" windowWidth="38080" windowHeight="20780" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bảng lương CB-NV" sheetId="5" r:id="rId1"/>
